--- a/src/attributions/attributions_ig_traj_472.xlsx
+++ b/src/attributions/attributions_ig_traj_472.xlsx
@@ -2140,52 +2140,52 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.329739404496266</v>
+        <v>0.003263077204211833</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03504119339422981</v>
+        <v>-0.00141124541409803</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1214288396130512</v>
+        <v>-0.001903932903192416</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3412800149898095</v>
+        <v>0.008201839509422824</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.03264159447913256</v>
+        <v>-0.002458456938013587</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1524622182915165</v>
+        <v>-0.005303944343143558</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -2194,22 +2194,22 @@
         <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1396134035405333</v>
+        <v>-0.0001963971575844862</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.121758370148059</v>
+        <v>-0.002781195431642098</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.04321609503297651</v>
+        <v>0.000292488500808637</v>
       </c>
       <c r="Z4" t="n">
         <v>-0</v>
@@ -2218,64 +2218,64 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1249471027082217</v>
+        <v>-0.002694396809160263</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.09290028588372584</v>
+        <v>-0.004323730278030581</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.009551449171841836</v>
+        <v>7.049812603438727e-05</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.05304893367817377</v>
+        <v>-0.0001650856995165801</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.02481576952397785</v>
+        <v>-0.0007273409743589906</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.03990594077420406</v>
+        <v>0.0002122882569461302</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.4300626958318378</v>
+        <v>0.009520455914579971</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
@@ -2284,25 +2284,25 @@
         <v>-0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1316586015883016</v>
+        <v>-0.0003327494094758217</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.2367618562604226</v>
+        <v>-0.0008573957930357617</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.05784729436501616</v>
+        <v>-0.001485765704116089</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.09655859131166444</v>
+        <v>-0.00169418577397984</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.00491563656916791</v>
+        <v>-0.0007050559123389079</v>
       </c>
       <c r="BJ4" t="n">
         <v>-0</v>
@@ -2326,25 +2326,25 @@
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.02380959970575595</v>
+        <v>0.00184817428507789</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.09058750890308123</v>
+        <v>0.005013564174328046</v>
       </c>
       <c r="BQ4" t="n">
         <v>-0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.08088684170115074</v>
+        <v>-0.0006147831478624437</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2353,52 +2353,52 @@
         <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1695629994592913</v>
+        <v>0.004109883164027381</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.07008340349157055</v>
+        <v>-0.0002793611321826788</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>-0.09825368390091734</v>
+        <v>-0.0006123848832971336</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.1188928319494688</v>
+        <v>-0.00127418146147072</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.006482807343268096</v>
+        <v>0.001108927738603325</v>
       </c>
       <c r="CI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.06010730973889362</v>
+        <v>0.0006816021296241791</v>
       </c>
       <c r="CK4" t="n">
         <v>-0</v>
@@ -2407,52 +2407,52 @@
         <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.02166201910361254</v>
+        <v>-0.002246208018200478</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.08705587596693716</v>
+        <v>0.0002872643572640362</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0.009381210141514478</v>
+        <v>-0.001071189521286152</v>
       </c>
       <c r="CT4" t="n">
         <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.1109536867465582</v>
+        <v>-0.001456300316120994</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.02108524125789343</v>
+        <v>0.0004732112656040681</v>
       </c>
       <c r="DA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.07456189657709507</v>
+        <v>0.001203547788199997</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
@@ -2461,10 +2461,10 @@
         <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.1268480063285294</v>
+        <v>-0.001882818675699053</v>
       </c>
       <c r="DG4" t="n">
         <v>-0</v>
@@ -2473,25 +2473,25 @@
         <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.03279659136603739</v>
+        <v>-0.002471095883927755</v>
       </c>
       <c r="DJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.02829375436085453</v>
+        <v>0.0004199770092343138</v>
       </c>
       <c r="DL4" t="n">
         <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.04475581583813636</v>
+        <v>0.0009291081293054114</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
@@ -2500,40 +2500,40 @@
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.0213358570801968</v>
+        <v>0.0003532300287055361</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.01252080455758541</v>
+        <v>0.002048879782821627</v>
       </c>
       <c r="DU4" t="n">
         <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.1441919400203852</v>
+        <v>-0.001957912492794864</v>
       </c>
       <c r="DY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ4" t="n">
         <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.02075014540769405</v>
+        <v>-2.084679303106118e-05</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.02893493117181658</v>
+        <v>0.002371289937518807</v>
       </c>
       <c r="ED4" t="n">
         <v>-0</v>
@@ -2542,10 +2542,10 @@
         <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.04865431621836851</v>
+        <v>-0.0008700236727566316</v>
       </c>
       <c r="EH4" t="n">
         <v>0</v>
@@ -2554,67 +2554,67 @@
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.01394573898531674</v>
+        <v>0.0004220162945058529</v>
       </c>
       <c r="EK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0882705186318011</v>
+        <v>-9.592571562509059e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.08398383984308844</v>
+        <v>-0.0006408066115857127</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
         <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.06764021736642659</v>
+        <v>-0.0005292047213799167</v>
       </c>
       <c r="ET4" t="n">
         <v>-0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0.05318502920887613</v>
+        <v>0.0006161138080700343</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.1157774992794783</v>
+        <v>-0.001939576355301558</v>
       </c>
       <c r="EZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.02892773787120006</v>
+        <v>0.0002297484541733339</v>
       </c>
       <c r="FC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.07841461717586996</v>
+        <v>0.0007967513740931445</v>
       </c>
       <c r="FE4" t="n">
         <v>-0</v>
@@ -2626,61 +2626,61 @@
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.0006104521923067727</v>
+        <v>0.001679970174545311</v>
       </c>
       <c r="FI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.03064759233492155</v>
+        <v>-0.001226227007651953</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.01270534177148304</v>
+        <v>-0.00156773301985587</v>
       </c>
       <c r="FN4" t="n">
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.01185681879651032</v>
+        <v>-0.0001401093114917</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.003182770382763528</v>
+        <v>0.0003377663078263469</v>
       </c>
       <c r="FU4" t="n">
         <v>-0</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.05014367255667615</v>
+        <v>0.002353560420768876</v>
       </c>
       <c r="FW4" t="n">
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.05286641408818149</v>
+        <v>-0.001000575343974719</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2689,19 +2689,19 @@
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
-        <v>-0.01026080957267931</v>
+        <v>0.002383249079096964</v>
       </c>
       <c r="GF4" t="n">
         <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3278,49 +3278,49 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5091494480061397</v>
+        <v>0.4136239349003106</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3485301208031067</v>
+        <v>-0.3754077310833911</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0284727737155516</v>
+        <v>0.01330022925948175</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4912127847526005</v>
+        <v>0.5790358217684737</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3587260694078647</v>
+        <v>-0.4402653029742247</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.09095316956961562</v>
+        <v>-0.04160277176488209</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3329,25 +3329,25 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2084676087803331</v>
+        <v>0.2117446107480994</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.01990441044588038</v>
+        <v>-0.05002326023263757</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1507249135335912</v>
+        <v>-0.03743988325086713</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -3356,52 +3356,52 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1343009941599115</v>
+        <v>-0.09198366000332278</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.002073694856067761</v>
+        <v>-0.1697350390120856</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.02020560601660971</v>
+        <v>-0.08193578748997662</v>
       </c>
       <c r="AG6" t="n">
         <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.02014367858576904</v>
+        <v>0.2274003774121407</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.1029768918859508</v>
+        <v>-0.08267936327576261</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.06786753816092971</v>
+        <v>0.1512609015644746</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3413,16 +3413,16 @@
         <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.5691320961418292</v>
+        <v>0.5187743950038455</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.08734423935739968</v>
+        <v>-0.2964608275016288</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.2112377287974646</v>
+        <v>-0.2153710375625711</v>
       </c>
       <c r="AY6" t="n">
         <v>-0</v>
@@ -3431,25 +3431,25 @@
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.04692878462369308</v>
+        <v>-0.07837199329312718</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.1061724320203671</v>
+        <v>-0.1380618558739102</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.1510069363401169</v>
+        <v>-0.08056900851986862</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -3467,100 +3467,100 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.04975314654346591</v>
+        <v>-0.09612382717522741</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.07218683978534621</v>
+        <v>0.08792684842113975</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.2159390774979577</v>
+        <v>-0.04932697812310359</v>
       </c>
       <c r="BQ6" t="n">
         <v>-0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.2324523010596126</v>
+        <v>0.4451729659264667</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.001483405045776278</v>
+        <v>-0.1777879068581754</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.118056094124087</v>
+        <v>-0.04167645792030682</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.1498218073074595</v>
+        <v>-0.1848469213612891</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.04904232665161382</v>
+        <v>0.2186484815751139</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.03456274985344952</v>
+        <v>-0.04875953207363614</v>
       </c>
       <c r="CI6" t="n">
         <v>0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.003804926626583998</v>
+        <v>-0.1368883367421784</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.2024311154284203</v>
+        <v>0.4693771374260143</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.1627437570133688</v>
+        <v>0.2421188198453166</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
@@ -3569,28 +3569,28 @@
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.1413390853596127</v>
+        <v>-0.1824688616829477</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.08896554690536274</v>
+        <v>0.2256115121624319</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.0318980974198192</v>
+        <v>-0.02342287383185355</v>
       </c>
       <c r="DA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
@@ -3602,46 +3602,46 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.1487632771264239</v>
+        <v>-0.2831549630447726</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.01139777975130363</v>
+        <v>0.1047110443098285</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.02053697068613517</v>
+        <v>-0.1370270396490442</v>
       </c>
       <c r="DJ6" t="n">
         <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.009796453535939539</v>
+        <v>-0.06561766849300629</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.1044470792762514</v>
+        <v>0.08675846612010144</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.08941235419648261</v>
+        <v>-0.01980260884986499</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3656,52 +3656,52 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.06933193973331173</v>
+        <v>-0.01633264277949773</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.001030245161517904</v>
+        <v>-0.1370064053875448</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.02605262215631136</v>
+        <v>-0.1282794951706789</v>
       </c>
       <c r="EB6" t="n">
         <v>0</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
         <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.1393556000527512</v>
+        <v>-0.1515488563169343</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.07232208030604852</v>
+        <v>0.185203111799694</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.09948211957468903</v>
+        <v>0.01056438942029912</v>
       </c>
       <c r="EK6" t="n">
         <v>0</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
@@ -3710,22 +3710,22 @@
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.1379944878047723</v>
+        <v>-0.1677068071429713</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.07432532504634967</v>
+        <v>0.09976804626376307</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01306958734054653</v>
+        <v>0.01735694272554248</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
@@ -3737,106 +3737,106 @@
         <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.1429284511864807</v>
+        <v>-0.2265030389330226</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.05728574452149764</v>
+        <v>0.2560256141648915</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.03616775326703744</v>
+        <v>-0.0415514076573648</v>
       </c>
       <c r="FC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.01709616414805581</v>
+        <v>-0.1709064969026202</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.1182627534924378</v>
+        <v>0.164744034266281</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.007539325529760442</v>
+        <v>0.07089589551989903</v>
       </c>
       <c r="FL6" t="n">
         <v>-0</v>
       </c>
       <c r="FM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
         <v>0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.007155240853427771</v>
+        <v>-0.03737773774320363</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.04404318752588997</v>
+        <v>0.05481494864401702</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.0009471295030820466</v>
+        <v>0.03516099488626419</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX6" t="n">
         <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.02108150734070569</v>
+        <v>-0.2640315116955106</v>
       </c>
       <c r="GA6" t="n">
         <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.1092687541328923</v>
+        <v>0.1418915581381389</v>
       </c>
       <c r="GC6" t="n">
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>-0</v>
@@ -3847,22 +3847,22 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2150578350293629</v>
+        <v>0.5409732706472929</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01645340715224021</v>
+        <v>-0.04309582758134686</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1308947601209474</v>
+        <v>-0.164762649197554</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
@@ -3874,25 +3874,25 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1909418860334726</v>
+        <v>0.8476833515762414</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0140178054614115</v>
+        <v>-0.1716967580669892</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.196740857338441</v>
+        <v>-0.2282824693251076</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0360417751128238</v>
+        <v>0.2326907201693391</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3910,64 +3910,64 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.02772172389922653</v>
+        <v>-0.1028033155457092</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01542599144316571</v>
+        <v>-0.03083393011205577</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.04165900070002719</v>
+        <v>0.04771806699816752</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02690986171699945</v>
+        <v>-0.4112339978691999</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.008944041364029333</v>
+        <v>-0.2030568612570967</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0181642336962472</v>
+        <v>0.1979855054677531</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02207058717779127</v>
+        <v>0.04240795101480054</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.04296436993933404</v>
+        <v>-0.1222745945212354</v>
       </c>
       <c r="AQ7" t="n">
         <v>-0</v>
@@ -3979,25 +3979,25 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1915880995013701</v>
+        <v>1.001987166022659</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.04081903667576706</v>
+        <v>-0.1743343349033867</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.1304412385956447</v>
+        <v>-0.3489458258091452</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
         <v>-0</v>
@@ -4009,73 +4009,73 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0634589460090953</v>
+        <v>-0.05028237808533269</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.02722480978178</v>
+        <v>-0.1680078878221594</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.03547320703105214</v>
+        <v>-0.030740303839889</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.07218930227266149</v>
+        <v>0.04797708050699603</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0225240198233073</v>
+        <v>0.1379856770177644</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.01887973810986917</v>
+        <v>-0.05109300434021567</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.08238613679381851</v>
+        <v>0.5691283718897604</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.01288587219781652</v>
+        <v>-0.03461557106499378</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.03874005323164887</v>
+        <v>-0.1585501557556218</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
@@ -4090,7 +4090,7 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.05372682999813318</v>
+        <v>-0.2689141884577717</v>
       </c>
       <c r="CF7" t="n">
         <v>0</v>
@@ -4099,52 +4099,52 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.01059554610538408</v>
+        <v>0.05388442612865815</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.04844803970177665</v>
+        <v>0.1355455593604897</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.01250994836524671</v>
+        <v>-0.5336637698696238</v>
       </c>
       <c r="CO7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.01171613527048285</v>
+        <v>0.2917872567784196</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.02495690536156621</v>
+        <v>0.2622562446649256</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.04238141544546808</v>
+        <v>-0.2566043124040472</v>
       </c>
       <c r="CX7" t="n">
         <v>-0</v>
@@ -4153,13 +4153,13 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.01113765369573175</v>
+        <v>0.01977437639597956</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.04947434628978348</v>
+        <v>0.1287127020368385</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,19 +4171,19 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.055801149694939</v>
+        <v>-0.1393000962653645</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH7" t="n">
         <v>-0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02681918981817489</v>
+        <v>-0.409568914377288</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0006365632438627889</v>
+        <v>0.06746480988417845</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4198,34 +4198,34 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.02621135989564245</v>
+        <v>-0.1329394226446696</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.009502134770895228</v>
+        <v>0.08072698742551263</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.002373259151957591</v>
+        <v>0.02912122980911021</v>
       </c>
       <c r="DT7" t="n">
         <v>0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW7" t="n">
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.03811624550060586</v>
+        <v>0.01470456531400925</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
@@ -4234,10 +4234,10 @@
         <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.02444706646769102</v>
+        <v>0.08516275516990623</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.03367442617572289</v>
+        <v>-0.1571037046451067</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
@@ -4252,7 +4252,7 @@
         <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.03500160317244068</v>
+        <v>-0.05796516739818667</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
@@ -4261,13 +4261,13 @@
         <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.005444306543112933</v>
+        <v>-0.05957551889129262</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.03097397112601947</v>
+        <v>0.03873381374656607</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>-0</v>
@@ -4276,22 +4276,22 @@
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.01866517939537641</v>
+        <v>-0.1166046084821691</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.0162777098814338</v>
+        <v>-0.12792757305314</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.03302400343697724</v>
+        <v>0.07141718066810351</v>
       </c>
       <c r="EU7" t="n">
         <v>-0</v>
@@ -4300,40 +4300,40 @@
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.04317217574984447</v>
+        <v>-0.2901841931841934</v>
       </c>
       <c r="EZ7" t="n">
         <v>0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.008032097811297795</v>
+        <v>-0.003099049293002029</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.04924469714554379</v>
+        <v>0.1212018584150898</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.003723148998297417</v>
+        <v>-0.3235153755335032</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
@@ -4342,25 +4342,25 @@
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.03569640809223598</v>
+        <v>0.1459688747393665</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.03829219061315533</v>
+        <v>0.0960518016856779</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.005141564379836466</v>
+        <v>-0.04938108045619978</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,28 +4369,28 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.00359831427893568</v>
+        <v>0.01624693529745101</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.04476079188392427</v>
+        <v>0.03226597112221115</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.01196289187896574</v>
+        <v>-0.1240193141113997</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,13 +4399,13 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.03766721033446196</v>
+        <v>-0.004680549827872841</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>0</v>
@@ -4982,19 +4982,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5505575158302849</v>
+        <v>0.02022510052521561</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1869647792384005</v>
+        <v>-0.006928703752659246</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5003,25 +5003,25 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5149652057416819</v>
+        <v>-0.005043776158198139</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4641490249175224</v>
+        <v>0.03016434642507839</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3729547018491681</v>
+        <v>-0.01808795078868428</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5030,34 +5030,34 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.8965998008890421</v>
+        <v>-0.01585714991556074</v>
       </c>
       <c r="R9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3027265110431657</v>
+        <v>0.01354992844199094</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3098495136277547</v>
+        <v>-0.01256211399707556</v>
       </c>
       <c r="X9" t="n">
         <v>-0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.1606343718799428</v>
+        <v>-0.005611752085623453</v>
       </c>
       <c r="AA9" t="n">
         <v>-0</v>
@@ -5066,16 +5066,16 @@
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.2627745170575702</v>
+        <v>-0.008983659925945839</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.1669092736456806</v>
+        <v>-0.01595747955785587</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -5084,34 +5084,34 @@
         <v>-0</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.2909016099233705</v>
+        <v>0.004457544016288209</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.08214723114619681</v>
+        <v>0.008785370109776536</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.01021063278407631</v>
+        <v>0.000833237477156679</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.1838548351434858</v>
+        <v>5.843180636982045e-06</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.078915996136951</v>
+        <v>0.03375584578679412</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
@@ -5129,43 +5129,43 @@
         <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.5258727655075109</v>
+        <v>-0.003048157680864702</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ9" t="n">
         <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.06336259656361527</v>
+        <v>-0.006478093018137992</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01991134648274931</v>
+        <v>-0.007083405614857153</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.3505226520307421</v>
+        <v>-0.01542995799336684</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
         <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-0.2956907425479152</v>
+        <v>-0.0006367791504493782</v>
       </c>
       <c r="BK9" t="n">
         <v>-0</v>
@@ -5174,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5895519703804922</v>
+        <v>0.008044974083039181</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
@@ -5183,16 +5183,16 @@
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.790217025246846</v>
+        <v>0.01669144787750192</v>
       </c>
       <c r="BQ9" t="n">
         <v>-0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.3115311776689687</v>
+        <v>0.006908210906927201</v>
       </c>
       <c r="BT9" t="n">
         <v>-0</v>
@@ -5201,16 +5201,16 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.4384984702045389</v>
+        <v>0.02526637485633385</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.2468215866436242</v>
+        <v>-0.001792507805297163</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -5219,25 +5219,25 @@
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.02024926544918096</v>
+        <v>-0.008928495592916258</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1701607192030334</v>
+        <v>-0.005443243369995176</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
         <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.009825753252642134</v>
+        <v>0.003406728871171406</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
@@ -5246,52 +5246,52 @@
         <v>-0</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.222154433126905</v>
+        <v>0.00338762873242641</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.4769470577926986</v>
+        <v>-0.009160314495568358</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.5214431199799255</v>
+        <v>0.01380054668107091</v>
       </c>
       <c r="CR9" t="n">
         <v>0</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0.1870520545733548</v>
+        <v>0.004784185870034054</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.1266707376238884</v>
+        <v>-0.005154187784140166</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.03455546703122087</v>
+        <v>0.00324593634489298</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
@@ -5300,52 +5300,52 @@
         <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.1090490024883095</v>
+        <v>0.005416920348832777</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.6576932160575604</v>
+        <v>-0.006307870613398357</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.08011393211851435</v>
+        <v>0.002031922485724958</v>
       </c>
       <c r="DJ9" t="n">
         <v>0</v>
       </c>
       <c r="DK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0.003695773152336445</v>
+        <v>0.000839222551930307</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.1654201834111794</v>
+        <v>-0.007806018746751903</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
         <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.07160916019072465</v>
+        <v>-0.002516925216297101</v>
       </c>
       <c r="DS9" t="n">
         <v>-0</v>
@@ -5354,16 +5354,16 @@
         <v>0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.1728890748335379</v>
+        <v>0.001308387467433841</v>
       </c>
       <c r="DV9" t="n">
         <v>-0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.02467225172215434</v>
+        <v>0.005451504590840886</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
@@ -5372,34 +5372,34 @@
         <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.06033550930618397</v>
+        <v>-0.008727386402273659</v>
       </c>
       <c r="EB9" t="n">
         <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0.1901833851573926</v>
+        <v>-0.01065752905693493</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.08248764377743978</v>
+        <v>0.004080066272676445</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.03422058370873715</v>
+        <v>-0.002703239886666777</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
@@ -5408,16 +5408,16 @@
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.2291878049697553</v>
+        <v>-0.001325835449156152</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.06178806831947702</v>
+        <v>-0.002751158608115832</v>
       </c>
       <c r="EQ9" t="n">
         <v>0</v>
@@ -5426,34 +5426,34 @@
         <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.1521157893971231</v>
+        <v>-0.005410070747815113</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
         <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>-0.02857731391542834</v>
+        <v>0.004811271118801269</v>
       </c>
       <c r="EW9" t="n">
         <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.1155600544641937</v>
+        <v>-0.005594817808393843</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.04580836798167895</v>
+        <v>0.0005254652992898707</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
@@ -5462,43 +5462,43 @@
         <v>-0</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.2046903393653886</v>
+        <v>0.005246457675171478</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.06857136971603112</v>
+        <v>-0.000462476441805401</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.1601554278660176</v>
+        <v>0.008849405761641048</v>
       </c>
       <c r="FL9" t="n">
         <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0.06975352473871771</v>
+        <v>-0.004649831460195624</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.01462485073293411</v>
+        <v>-0.0009151103857993113</v>
       </c>
       <c r="FR9" t="n">
         <v>-0</v>
@@ -5507,34 +5507,34 @@
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.04005883588233029</v>
+        <v>0.002078151804504832</v>
       </c>
       <c r="FU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0.1814698235212332</v>
+        <v>0.001575405430163655</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.3608240616142978</v>
+        <v>-0.009441187358177481</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
         <v>0</v>
@@ -5543,60 +5543,60 @@
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>-0.3300197345782492</v>
+        <v>-0.002913876902069628</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.3201069958423193</v>
+        <v>-0.2585333049876861</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6320091514483427</v>
+        <v>0.5529630661764842</v>
       </c>
       <c r="C10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2358875639782447</v>
+        <v>-0.1370477932482038</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2234377661255625</v>
+        <v>-0.1945093181156659</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5148734774393224</v>
+        <v>0.7789314361779236</v>
       </c>
       <c r="L10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5117548087763245</v>
+        <v>-0.1693123292857018</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -5605,19 +5605,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.02206938997238747</v>
+        <v>0.1032679108146265</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3670833177358572</v>
+        <v>0.001743118526600411</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1794759103722527</v>
+        <v>0.004585759789369774</v>
       </c>
       <c r="X10" t="n">
         <v>-0</v>
@@ -5626,124 +5626,124 @@
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.02078766065777697</v>
+        <v>-0.08971185440583865</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1922671714228789</v>
+        <v>-0.001805183975518334</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.07866378253460937</v>
+        <v>-0.1090909008757809</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.1146266779855946</v>
+        <v>-0.01570308135232287</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.2257917011179836</v>
+        <v>0.1428413994475831</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.01182773443055132</v>
+        <v>-0.1511399933195828</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.2300887619716731</v>
+        <v>-0.01714321957139878</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.7732805470806201</v>
+        <v>0.4222970165902983</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.364409427006545</v>
+        <v>-0.2647384427048711</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.212229323468509</v>
+        <v>-0.2306234121215119</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.05439842369843822</v>
+        <v>0.1254069940946709</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.4294288674343181</v>
+        <v>0.004804474852922525</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0.09121987303078703</v>
+        <v>0.08064405063759986</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.1449943613813964</v>
+        <v>0.2220026589409974</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,13 +5752,13 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.4038474477770921</v>
+        <v>0.171720570171432</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5767,49 +5767,49 @@
         <v>-0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.1237834296615499</v>
+        <v>0.08834896839037557</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.4173557391239679</v>
+        <v>0.3337209369970852</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.04247553644818637</v>
+        <v>-0.04612030204306114</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.05826561555414225</v>
+        <v>0.08881032044358303</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.134598138210163</v>
+        <v>-0.2173739381412612</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.007093524758107107</v>
+        <v>0.02342894875153484</v>
       </c>
       <c r="CI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ10" t="n">
         <v>-0</v>
@@ -5821,76 +5821,76 @@
         <v>-0</v>
       </c>
       <c r="CM10" t="n">
-        <v>-0.3061325532497021</v>
+        <v>-0.06029070960127137</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.1297606980549161</v>
+        <v>-0.4038189852821087</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.3414984320443166</v>
+        <v>-0.04281033032491656</v>
       </c>
       <c r="CR10" t="n">
         <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
         <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.02728733132185802</v>
+        <v>0.07510496898136709</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.1509163342354331</v>
+        <v>-0.2256094123070137</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0227652766982379</v>
+        <v>-0.01524980823592633</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.3088086672933626</v>
+        <v>0.1058392357186666</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.5213418263506325</v>
+        <v>-0.3568024217822677</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.06216853613195463</v>
+        <v>0.0001495289018542181</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
         <v>0</v>
@@ -5899,13 +5899,13 @@
         <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0.1754732522984578</v>
+        <v>-0.05700532481184557</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.2226355621161783</v>
+        <v>-0.1525280825747158</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
@@ -5914,25 +5914,25 @@
         <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.05583095638048067</v>
+        <v>-0.01968677114993017</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT10" t="n">
         <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0.05755652401285949</v>
+        <v>0.1938920910948649</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.1397478414711541</v>
+        <v>0.1256952038676695</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,25 +5941,25 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.1211244249335567</v>
+        <v>0.05184435047691616</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0.07579577565637186</v>
+        <v>-0.007783920749178976</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.19335791219972</v>
+        <v>-0.1357277643634022</v>
       </c>
       <c r="EH10" t="n">
         <v>0</v>
@@ -5968,7 +5968,7 @@
         <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.01535623056011122</v>
+        <v>-0.0495159243981384</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5983,19 +5983,19 @@
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>-0.03335098049438633</v>
+        <v>-0.09253197567582172</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.1115873081619997</v>
+        <v>-0.1382640812294951</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
         <v>0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.03931680993140869</v>
+        <v>-0.02106927144955822</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
@@ -6007,13 +6007,13 @@
         <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.05307678637330294</v>
+        <v>0.07933568119763411</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.139754193369757</v>
+        <v>-0.2781996045761439</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
@@ -6022,25 +6022,25 @@
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.0501612256633138</v>
+        <v>-0.02736578918901152</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>-0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.1945824355983657</v>
+        <v>0.07077275099166266</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.08902586162004682</v>
+        <v>0.01281679223584149</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
@@ -6049,7 +6049,7 @@
         <v>0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.08871961031104381</v>
+        <v>0.08655807250323579</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
@@ -6064,37 +6064,37 @@
         <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>-0.003265344563816009</v>
+        <v>-0.09611510256817225</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.03363000358762867</v>
+        <v>0.02815750246456566</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.01053009293721037</v>
+        <v>0.04915292261915805</v>
       </c>
       <c r="FU10" t="n">
         <v>-0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
         <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0.07931406167625607</v>
+        <v>0.04615210544553407</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.1912028072345067</v>
+        <v>-0.1910668739422346</v>
       </c>
       <c r="GA10" t="n">
         <v>-0</v>
@@ -6106,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
@@ -6115,7 +6115,7 @@
         <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,49 +6123,49 @@
         <v>-0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6394727265793381</v>
+        <v>0.1515170800182909</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2867283245309152</v>
+        <v>-0.1785828054220088</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3522750555858268</v>
+        <v>-0.1529373627829677</v>
       </c>
       <c r="H11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4484784375792149</v>
+        <v>0.2332934832050888</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3085273774915624</v>
+        <v>-0.1899268769631863</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3103309998831958</v>
+        <v>-0.2066543347703509</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6177,49 +6177,49 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2111122096653329</v>
+        <v>0.0373481744772048</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.260498669818286</v>
+        <v>-0.05229556296700465</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.04222317993537852</v>
+        <v>0.06478719294918348</v>
       </c>
       <c r="Z11" t="n">
         <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.2368052384134104</v>
+        <v>-0.09351317470368595</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.07470035197579998</v>
+        <v>-0.180204740810824</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.02747525251334188</v>
+        <v>0.02957065424390622</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
@@ -6228,10 +6228,10 @@
         <v>-0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.07382749035709109</v>
+        <v>0.1439516651590127</v>
       </c>
       <c r="AM11" t="n">
         <v>-0</v>
@@ -6240,16 +6240,16 @@
         <v>-0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.01421597102856941</v>
+        <v>0.03010748215956065</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.08088867344575527</v>
+        <v>0.04590629885091129</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>-0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.7111857861412095</v>
+        <v>0.4021916197562682</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
@@ -6267,40 +6267,40 @@
         <v>-0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.01144157846163145</v>
+        <v>-0.005874328122446166</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.194743821901728</v>
+        <v>0.009625491348965206</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.1386630283508359</v>
+        <v>-0.1451944011056095</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF11" t="n">
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1537017720514165</v>
+        <v>-0.1910272237340425</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0.1719667992132358</v>
+        <v>-0.07176677171514768</v>
       </c>
       <c r="BJ11" t="n">
         <v>0</v>
@@ -6309,10 +6309,10 @@
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.129921773323781</v>
+        <v>-0.01045616499857672</v>
       </c>
       <c r="BN11" t="n">
         <v>0</v>
@@ -6321,13 +6321,13 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.2753612797122582</v>
+        <v>0.1159085671766333</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.05320709510504697</v>
+        <v>0.0861933956422469</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6339,34 +6339,34 @@
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.2612426899628142</v>
+        <v>0.2330073090554946</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.0256976584708545</v>
+        <v>-0.03630570722091228</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>-0.05610276921408027</v>
+        <v>0.004564153819095945</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1634144912905043</v>
+        <v>-0.06216006196294081</v>
       </c>
       <c r="CF11" t="n">
         <v>0</v>
@@ -6375,13 +6375,13 @@
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.04919595272246327</v>
+        <v>0.05979204259414948</v>
       </c>
       <c r="CI11" t="n">
         <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.0819156380931783</v>
+        <v>0.01955000856643379</v>
       </c>
       <c r="CK11" t="n">
         <v>-0</v>
@@ -6390,25 +6390,25 @@
         <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.2291046544859701</v>
+        <v>-0.179750774142917</v>
       </c>
       <c r="CO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.1671749971551101</v>
+        <v>0.09763531737393522</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0.007678939358759736</v>
+        <v>-0.1293977393322897</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
@@ -6417,10 +6417,10 @@
         <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.1318684575569194</v>
+        <v>-0.06370295787895482</v>
       </c>
       <c r="CX11" t="n">
         <v>-0</v>
@@ -6429,13 +6429,13 @@
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.04670968884100793</v>
+        <v>0.06014662710045873</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.07954506941689378</v>
+        <v>0.03223899505241039</v>
       </c>
       <c r="DC11" t="n">
         <v>0</v>
@@ -6444,52 +6444,52 @@
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.4164543422767302</v>
+        <v>-0.08455966312271353</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.04491044981547947</v>
+        <v>0.01159521707168701</v>
       </c>
       <c r="DJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK11" t="n">
-        <v>-0.1382195987126834</v>
+        <v>-0.05588306133124435</v>
       </c>
       <c r="DL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.07751523479649475</v>
+        <v>-0.02926145622109126</v>
       </c>
       <c r="DP11" t="n">
         <v>0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.06365130329668778</v>
+        <v>0.122487145166994</v>
       </c>
       <c r="DS11" t="n">
         <v>-0</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0.01293864051259389</v>
+        <v>0.0681238186543313</v>
       </c>
       <c r="DU11" t="n">
         <v>-0</v>
@@ -6498,52 +6498,52 @@
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1439916073538324</v>
+        <v>0.02126601434875945</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.09670330927506753</v>
+        <v>-0.07216024440151905</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0.006568243495610016</v>
+        <v>-0.002395241609161545</v>
       </c>
       <c r="ED11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.05240041749899019</v>
+        <v>-0.06448903457779688</v>
       </c>
       <c r="EH11" t="n">
         <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.09775697819205766</v>
+        <v>0.005616051653930747</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.1027576022496439</v>
+        <v>-0.02655364625365641</v>
       </c>
       <c r="EM11" t="n">
         <v>-0</v>
@@ -6552,52 +6552,52 @@
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.06806216159196697</v>
+        <v>-0.03691582877280806</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.006981400744815148</v>
+        <v>0.003320796803728783</v>
       </c>
       <c r="ET11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0.01194485847981911</v>
+        <v>-0.04974128842587698</v>
       </c>
       <c r="EV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1408571109494271</v>
+        <v>-0.06719123244635244</v>
       </c>
       <c r="EZ11" t="n">
         <v>0</v>
       </c>
       <c r="FA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.04427624392009453</v>
+        <v>0.04232915060041374</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.07958314407140828</v>
+        <v>0.01495462210776252</v>
       </c>
       <c r="FE11" t="n">
         <v>-0</v>
@@ -6606,25 +6606,25 @@
         <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.04479719748852456</v>
+        <v>-0.06034077897986307</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.1205907842430766</v>
+        <v>-0.02986971132053118</v>
       </c>
       <c r="FL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.05932030006412938</v>
+        <v>-0.03485937829643673</v>
       </c>
       <c r="FN11" t="n">
         <v>-0</v>
@@ -6633,10 +6633,10 @@
         <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.01015269760119976</v>
+        <v>-0.02947742660749332</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,28 +6645,28 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.02256102689127081</v>
+        <v>-0.01428312124510887</v>
       </c>
       <c r="FU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.0001663203915489765</v>
+        <v>0.09597184008323505</v>
       </c>
       <c r="FW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX11" t="n">
         <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.1106901193209862</v>
+        <v>-0.07249558774204581</v>
       </c>
       <c r="GA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
@@ -6675,10 +6675,10 @@
         <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
-        <v>-0.06442879973015084</v>
+        <v>0.06998418932270901</v>
       </c>
       <c r="GF11" t="n">
         <v>-0</v>
@@ -6689,10 +6689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>1.109002510642023</v>
+        <v>0.8057382917230139</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -6701,7 +6701,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3620317104367999</v>
+        <v>-0.4576070314345054</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6713,13 +6713,13 @@
         <v>-0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5441075947901269</v>
+        <v>-0.1858729010367829</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8208495368911543</v>
+        <v>1.042385439110252</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -6728,115 +6728,115 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3815344216259309</v>
+        <v>-0.5267790538272202</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.4957252327836016</v>
+        <v>-0.1679277293185162</v>
       </c>
       <c r="S12" t="n">
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.343785183382271</v>
+        <v>0.09299445850552605</v>
       </c>
       <c r="U12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03604885916899599</v>
+        <v>-0.2032318721017696</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z12" t="n">
         <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.1046669798180174</v>
+        <v>-0.181649749038749</v>
       </c>
       <c r="AB12" t="n">
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.3276670619599004</v>
+        <v>0.103616847664272</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.08144003468929426</v>
+        <v>-0.2032451122506458</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
         <v>-0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0.02599383779852389</v>
+        <v>0.01503392782587149</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.1728023585219027</v>
+        <v>0.2755197080713718</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.005978002587623073</v>
+        <v>0.07529302089585101</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0.03660857206532703</v>
+        <v>-0.03901436954808084</v>
       </c>
       <c r="AT12" t="n">
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.064637479373003</v>
+        <v>1.104277197311176</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.08634485769827283</v>
+        <v>-0.1716910971726517</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
@@ -6845,16 +6845,16 @@
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>-0.3078297614297999</v>
+        <v>-0.002469566189113378</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1780003823063034</v>
+        <v>-0.1516723463170842</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,7 +6863,7 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.3603540251150389</v>
+        <v>-0.2444420471881887</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,16 +6872,16 @@
         <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0.2575292020879729</v>
+        <v>-0.05346438511276832</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1226796082448601</v>
+        <v>0.1237868246197611</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
@@ -6890,25 +6890,25 @@
         <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.432846132630344</v>
+        <v>0.2446556712175755</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0.009489365849392245</v>
+        <v>0.109805446704583</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.546285728803616</v>
+        <v>0.5693032835191646</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
@@ -6917,25 +6917,25 @@
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.08227314981920483</v>
+        <v>-0.1996224939744918</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0.1041760068704934</v>
+        <v>-0.1662091553644489</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.2590944111098931</v>
+        <v>-0.3543258058344872</v>
       </c>
       <c r="CF12" t="n">
         <v>-0</v>
@@ -6944,37 +6944,37 @@
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.01560623151484463</v>
+        <v>0.1056803976698626</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.1839378920199971</v>
+        <v>0.07741826415011485</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.3250856545392993</v>
+        <v>-0.6245055263053634</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
         <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.2970223661660355</v>
+        <v>0.03607912319416406</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6983,49 +6983,49 @@
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.06131974582781816</v>
+        <v>0.008200972626623452</v>
       </c>
       <c r="CV12" t="n">
         <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.2241515681933035</v>
+        <v>-0.3382672069974696</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.02473182254519969</v>
+        <v>0.0850783579599108</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.1406341338322815</v>
+        <v>0.09133186133101216</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.5652883986343037</v>
+        <v>-0.2235119059635537</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
         <v>-0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.1323822313163398</v>
+        <v>-0.01829276429577338</v>
       </c>
       <c r="DJ12" t="n">
         <v>-0</v>
@@ -7037,22 +7037,22 @@
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.04357367690794176</v>
+        <v>-0.05770101523973345</v>
       </c>
       <c r="DN12" t="n">
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.1446952456697684</v>
+        <v>-0.1665589537826136</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.006620924120542991</v>
+        <v>0.05170368488937838</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
@@ -7061,16 +7061,16 @@
         <v>0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0.03017930374928252</v>
+        <v>-0.1805678711344889</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.1879251761322843</v>
+        <v>0.2571191806937556</v>
       </c>
       <c r="DY12" t="n">
         <v>-0</v>
@@ -7079,79 +7079,79 @@
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.09381227894990062</v>
+        <v>-0.07204335158484623</v>
       </c>
       <c r="EB12" t="n">
         <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.0134657610443933</v>
+        <v>0.2208004499992672</v>
       </c>
       <c r="EF12" t="n">
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.03188525121688013</v>
+        <v>-0.1679226203046627</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.06467700355726905</v>
+        <v>0.00297280947644209</v>
       </c>
       <c r="EK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.2407440500675926</v>
+        <v>0.04955186829153677</v>
       </c>
       <c r="EO12" t="n">
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.1636879045420602</v>
+        <v>-0.1867660784185236</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.03115582351661013</v>
+        <v>0.04020943626790926</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>-0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.02288997964432253</v>
+        <v>0.1321742322290466</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.2604506133485941</v>
+        <v>-0.3976481536409839</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
@@ -7160,100 +7160,100 @@
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.005492865132659888</v>
+        <v>0.06586781392941472</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.1301566168033032</v>
+        <v>0.1026163733690383</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.122680146768897</v>
+        <v>-0.1395023988703115</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.1038613188688495</v>
+        <v>-0.01866983865406524</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>-0.1520485817299997</v>
+        <v>-0.08742228420918922</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.01495981794070308</v>
+        <v>-0.01527578241722053</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01107967561369109</v>
+        <v>0.03631628878809224</v>
       </c>
       <c r="FU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.05630249728732539</v>
+        <v>-0.0133430283011477</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.2659828494227312</v>
+        <v>-0.1899075366752729</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0.0553870713158484</v>
+        <v>0.008725589054809592</v>
       </c>
     </row>
     <row r="13">
@@ -7830,16 +7830,16 @@
         <v>-0</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.5263589242471366</v>
+        <v>-0.5631578618896709</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6561602907780183</v>
+        <v>0.2732706334145816</v>
       </c>
       <c r="D14" t="n">
         <v>-0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1462611492574238</v>
+        <v>0.2674470399554658</v>
       </c>
       <c r="F14" t="n">
         <v>-0</v>
@@ -7857,19 +7857,19 @@
         <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4469623166147181</v>
+        <v>-0.6941938154356907</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4752960060020092</v>
+        <v>0.2824808025072283</v>
       </c>
       <c r="M14" t="n">
         <v>-0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5022363781143702</v>
+        <v>0.2494001338071679</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -7881,19 +7881,19 @@
         <v>-0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1772453957995592</v>
+        <v>-0.1142947920595935</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.02177110209064688</v>
+        <v>-0.07327817311306169</v>
       </c>
       <c r="V14" t="n">
         <v>-0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.05584199838317818</v>
+        <v>-0.03353824052204277</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -7902,79 +7902,79 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB14" t="n">
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.248185614094744</v>
+        <v>-0.02623212539862257</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.02456346957911471</v>
+        <v>0.1407817637722961</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.1937193304210485</v>
+        <v>0.01496337777619614</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>-0</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.2748260904433181</v>
+        <v>-0.2043247819273134</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0955866649607692</v>
+        <v>0.02024014149231052</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.02093089353460846</v>
+        <v>-0.223362240804027</v>
       </c>
       <c r="AP14" t="n">
         <v>-0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0.6665477772920931</v>
+        <v>-0.6372113743753836</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.4128272211552594</v>
+        <v>0.01783535048790851</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.1544546201947827</v>
+        <v>0.04227646938157681</v>
       </c>
       <c r="AY14" t="n">
         <v>-0</v>
@@ -7983,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
@@ -7992,16 +7992,16 @@
         <v>-0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.01510141920161883</v>
+        <v>0.2579796255570939</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.2102066447069666</v>
+        <v>0.2094293480203513</v>
       </c>
       <c r="BF14" t="n">
         <v>-0</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.5684338243253173</v>
+        <v>0.2936535794859261</v>
       </c>
       <c r="BH14" t="n">
         <v>-0</v>
@@ -8019,22 +8019,22 @@
         <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0.1577480301074134</v>
+        <v>0.03496683066462872</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0842575046735657</v>
+        <v>-0.01942164198606022</v>
       </c>
       <c r="BO14" t="n">
         <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.3468793253000507</v>
+        <v>0.003445786322469074</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS14" t="n">
         <v>0</v>
@@ -8046,19 +8046,19 @@
         <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0.1960200829614315</v>
+        <v>-0.3748113828984223</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.3169478564083854</v>
+        <v>0.01710225989311437</v>
       </c>
       <c r="BX14" t="n">
         <v>-0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.05198104557020931</v>
+        <v>0.003601708479361075</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA14" t="n">
         <v>0</v>
@@ -8070,19 +8070,19 @@
         <v>-0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.1217406627379084</v>
+        <v>0.257226405601484</v>
       </c>
       <c r="CF14" t="n">
-        <v>-0.05553385505954265</v>
+        <v>-0.08536356688920306</v>
       </c>
       <c r="CG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.05840003207354124</v>
+        <v>-0.0455146348700882</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
@@ -8091,7 +8091,7 @@
         <v>0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
@@ -8100,16 +8100,16 @@
         <v>-0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0711566276155803</v>
+        <v>0.3372475537344869</v>
       </c>
       <c r="CO14" t="n">
-        <v>-0.01888796609448625</v>
+        <v>-0.07694899926479708</v>
       </c>
       <c r="CP14" t="n">
         <v>0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.2129079523229254</v>
+        <v>-0.1096120757069551</v>
       </c>
       <c r="CR14" t="n">
         <v>0</v>
@@ -8118,25 +8118,25 @@
         <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
         <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.07697652879253047</v>
+        <v>0.2421206035954034</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0.06853611783316689</v>
+        <v>-0.06827791247726911</v>
       </c>
       <c r="CY14" t="n">
         <v>-0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.07306996379440737</v>
+        <v>-0.04127070921722357</v>
       </c>
       <c r="DA14" t="n">
         <v>-0</v>
@@ -8145,7 +8145,7 @@
         <v>-0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
         <v>-0</v>
@@ -8154,73 +8154,73 @@
         <v>-0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.202821078365236</v>
+        <v>0.07019791562354652</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.05982553087285746</v>
+        <v>-0.04057503848845449</v>
       </c>
       <c r="DH14" t="n">
         <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.1601148250253166</v>
+        <v>0.01972755220594033</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
         <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.01590764248874078</v>
+        <v>0.1378029806118728</v>
       </c>
       <c r="DP14" t="n">
-        <v>-0.1468291164307829</v>
+        <v>-0.07757313147299982</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.08027537761310356</v>
+        <v>0.001172583039864709</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>0</v>
       </c>
       <c r="DU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV14" t="n">
         <v>-0</v>
       </c>
       <c r="DW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.01492008710118048</v>
+        <v>-0.1469649384969493</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.2141407255741934</v>
+        <v>-0.05591836991055507</v>
       </c>
       <c r="DZ14" t="n">
         <v>0</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.03275142293197108</v>
+        <v>0.06442700053325329</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC14" t="n">
         <v>-0</v>
@@ -8232,19 +8232,19 @@
         <v>0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.02751634740164072</v>
+        <v>0.1743412624761679</v>
       </c>
       <c r="EH14" t="n">
-        <v>-0.01088212341903618</v>
+        <v>0.07020859540515499</v>
       </c>
       <c r="EI14" t="n">
         <v>0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.1320169680259974</v>
+        <v>-0.04876339128998497</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
@@ -8262,52 +8262,52 @@
         <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.07524382686824914</v>
+        <v>0.1734197179600232</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.06860221017485242</v>
+        <v>0.01883251155506685</v>
       </c>
       <c r="ER14" t="n">
         <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.1268866366518944</v>
+        <v>-0.06660686884642783</v>
       </c>
       <c r="ET14" t="n">
         <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
         <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.09343948052611313</v>
+        <v>0.2895237534027905</v>
       </c>
       <c r="EZ14" t="n">
-        <v>-0.05612614776440268</v>
+        <v>-0.07437047190047702</v>
       </c>
       <c r="FA14" t="n">
         <v>0</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.08105116936126079</v>
+        <v>-0.05918123598659694</v>
       </c>
       <c r="FC14" t="n">
         <v>0</v>
       </c>
       <c r="FD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
         <v>0</v>
@@ -8316,90 +8316,90 @@
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.1519325408030751</v>
+        <v>0.06187777404642715</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.1905831366988929</v>
+        <v>0.1218828352101071</v>
       </c>
       <c r="FJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.1886199290958864</v>
+        <v>0.1175291277334836</v>
       </c>
       <c r="FL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN14" t="n">
         <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP14" t="n">
         <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-1.264573956750177e-05</v>
+        <v>0.001619905656652519</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0.0773749085844959</v>
+        <v>-0.0002143237558384262</v>
       </c>
       <c r="FS14" t="n">
         <v>0</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.006970377742108164</v>
+        <v>-0.009797689040986993</v>
       </c>
       <c r="FU14" t="n">
         <v>0</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
         <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.003959591714771491</v>
+        <v>0.148512724741184</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.07444906610766343</v>
+        <v>0.113605793512404</v>
       </c>
       <c r="GB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE14" t="n">
         <v>0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.4193913524864991</v>
+        <v>-0.1760098734128454</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
@@ -8408,13 +8408,13 @@
         <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05735580291277353</v>
+        <v>0.05108108844583922</v>
       </c>
       <c r="F15" t="n">
-        <v>1.035147378343664</v>
+        <v>0.3398388795887985</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -8423,10 +8423,10 @@
         <v>-0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3519979926276593</v>
+        <v>-0.2277580473879689</v>
       </c>
       <c r="L15" t="n">
         <v>-0</v>
@@ -8435,25 +8435,25 @@
         <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.09719004825977103</v>
+        <v>0.1447550812273173</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7970956499911807</v>
+        <v>0.4432223597338499</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.03687451535882046</v>
+        <v>-0.07309131683258129</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
@@ -8462,13 +8462,13 @@
         <v>-0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1586308321541925</v>
+        <v>0.06205921821999616</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0933737787487529</v>
+        <v>0.09502427196030597</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -8477,22 +8477,22 @@
         <v>-0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.05761432983598488</v>
+        <v>0.02209219360342318</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0562873858139684</v>
+        <v>0.1551542764489358</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.05388466812728854</v>
+        <v>-0.0196039151966622</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
@@ -8501,13 +8501,13 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK15" t="n">
         <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.02929476488184719</v>
+        <v>-0.0347775688400293</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
@@ -8516,13 +8516,13 @@
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.01413938302415433</v>
+        <v>-0.00591116684673616</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.1717182657779255</v>
+        <v>0.07993475310292625</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -8531,37 +8531,37 @@
         <v>-0</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.3856684663823999</v>
+        <v>-0.4746227102226953</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW15" t="n">
         <v>-0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.2701084146152701</v>
+        <v>0.113871784394312</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.7171740509332811</v>
+        <v>0.2673083526080413</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.1219493344531752</v>
+        <v>0.1293530938500242</v>
       </c>
       <c r="BE15" t="n">
         <v>-0</v>
@@ -8570,10 +8570,10 @@
         <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.04847327529219924</v>
+        <v>0.04781527348638306</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.1385884201723515</v>
+        <v>0.002477034467663897</v>
       </c>
       <c r="BI15" t="n">
         <v>-0</v>
@@ -8582,52 +8582,52 @@
         <v>0</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.1830357960083081</v>
+        <v>-0.08663745212382837</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.06522403184129982</v>
+        <v>-0.05998477186128948</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.06617832325918234</v>
+        <v>-0.02928035250940444</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT15" t="n">
         <v>-0</v>
       </c>
       <c r="BU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.146696166919964</v>
+        <v>-0.1381189772854395</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
         <v>-0</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.09210515393069182</v>
+        <v>0.03099274849493336</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.3471341093134395</v>
+        <v>0.1776270354316332</v>
       </c>
       <c r="CA15" t="n">
         <v>0</v>
@@ -8636,40 +8636,40 @@
         <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
         <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.1194684396780524</v>
+        <v>0.08918075099011855</v>
       </c>
       <c r="CF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.01869627851348746</v>
+        <v>-0.04216184501575252</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0.160687091430458</v>
+        <v>-0.06515636968803766</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
         <v>-0</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM15" t="n">
         <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.005543524447955893</v>
+        <v>0.0943336086765339</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
@@ -8678,16 +8678,16 @@
         <v>0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.2375529704357506</v>
+        <v>-0.09981970475303394</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.03067271553226303</v>
+        <v>-0.04909760105272534</v>
       </c>
       <c r="CS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU15" t="n">
         <v>0</v>
@@ -8696,73 +8696,73 @@
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.09086067261758959</v>
+        <v>0.0789224294932242</v>
       </c>
       <c r="CX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY15" t="n">
         <v>-0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.01162367555539271</v>
+        <v>-0.04690765775715289</v>
       </c>
       <c r="DA15" t="n">
-        <v>-0.1696518128706331</v>
+        <v>-0.09382844649885944</v>
       </c>
       <c r="DB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC15" t="n">
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE15" t="n">
         <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1257059367863718</v>
+        <v>0.07301724956976149</v>
       </c>
       <c r="DG15" t="n">
         <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.2932217290319694</v>
+        <v>0.1042843860815658</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.007581230313567193</v>
+        <v>-0.01795522942630319</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.02834621083858908</v>
+        <v>-0.05633355891906135</v>
       </c>
       <c r="DP15" t="n">
         <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.05154513664228862</v>
+        <v>0.05769492578151223</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0.06521450546557701</v>
+        <v>-0.08392929455942352</v>
       </c>
       <c r="DT15" t="n">
         <v>0</v>
@@ -8771,13 +8771,13 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.09323359104688517</v>
+        <v>0.1038601844819852</v>
       </c>
       <c r="DY15" t="n">
         <v>0</v>
@@ -8786,10 +8786,10 @@
         <v>0</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.07898271216613939</v>
+        <v>0.00107141392389684</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0.1188386473744737</v>
+        <v>0.01934445134179449</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
@@ -8798,31 +8798,31 @@
         <v>-0</v>
       </c>
       <c r="EE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF15" t="n">
         <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.0637277564739325</v>
+        <v>0.06948229255083882</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.02096748542565594</v>
+        <v>-0.06157488572586131</v>
       </c>
       <c r="EK15" t="n">
-        <v>-0.1142137547457192</v>
+        <v>0.02630154983530177</v>
       </c>
       <c r="EL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN15" t="n">
         <v>0</v>
@@ -8831,73 +8831,73 @@
         <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.07538477723198488</v>
+        <v>0.04945185436363656</v>
       </c>
       <c r="EQ15" t="n">
         <v>0</v>
       </c>
       <c r="ER15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.05016986799317925</v>
+        <v>-0.04407372845362763</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0.04148253538983084</v>
+        <v>0.03989663103855391</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
         <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.08269910872492069</v>
+        <v>0.1000331103532043</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.03558840908236152</v>
+        <v>-0.0178894925286274</v>
       </c>
       <c r="FC15" t="n">
-        <v>-0.1572501519018988</v>
+        <v>-0.08064123985832243</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
         <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
         <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.007814731657287362</v>
+        <v>-0.07691670110214546</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
         <v>0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.04383720571030961</v>
+        <v>-0.001812324568310594</v>
       </c>
       <c r="FL15" t="n">
-        <v>-0.1399684100677052</v>
+        <v>-0.1279575096372529</v>
       </c>
       <c r="FM15" t="n">
         <v>-0</v>
@@ -8906,31 +8906,31 @@
         <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
         <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.003516116555176326</v>
+        <v>0.02803476455159675</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.08088923460527922</v>
+        <v>-0.07429806703954973</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0.1594481572666532</v>
+        <v>0.1028504445231461</v>
       </c>
       <c r="FV15" t="n">
         <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX15" t="n">
         <v>-0</v>
@@ -8939,19 +8939,19 @@
         <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.04086205755550364</v>
+        <v>0.05567520023880203</v>
       </c>
       <c r="GA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.07005114483952433</v>
+        <v>-0.04728610900655472</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
